--- a/docs/sprint1/backlog.xlsx
+++ b/docs/sprint1/backlog.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Спринт 1" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="364">
   <si>
     <t xml:space="preserve">Таблиця 1. Беклог вимог (user stories)</t>
   </si>
@@ -79,7 +79,7 @@
     <t xml:space="preserve">High</t>
   </si>
   <si>
-    <t xml:space="preserve">A = P·i / (1 − (1+i)^−n), i = річна ставка / 12 / 100; округлення до 0,01 HALF_UP; контрольний приклад (орієнтовний, до підстановки меж BL — див. В1): P = 100 000, 20 % річних, n = 12 → A = 9 263,45, переплата = 11 161,40</t>
+    <t xml:space="preserve">A = P·i / (1 − (1+i)^−n), i = річна ставка / 12 / 100; округлення до 0,01 HALF_UP; контрольний приклад (орієнтовний, до підстановки меж BL - див. В1): P = 100 000, 20 % річних, n = 12 → A = 9 263,45, переплата = 11 161,40</t>
   </si>
   <si>
     <t xml:space="preserve">чернетка</t>
@@ -205,7 +205,7 @@
     <t xml:space="preserve">час відповіді не більший за &lt;значення з SRS, розділ P-&gt;; три результати: схвалено / відмова / ручний розгляд; текст рішення непорожній</t>
   </si>
   <si>
-    <t xml:space="preserve">Попереднє рішення «за кілька секунд» — окремо назване очікування</t>
+    <t xml:space="preserve">Попереднє рішення «за кілька секунд» - окремо назване очікування</t>
   </si>
   <si>
     <t xml:space="preserve">US-09</t>
@@ -217,7 +217,7 @@
     <t xml:space="preserve">зрозуміти, що змінити перед повторною заявкою</t>
   </si>
   <si>
-    <t xml:space="preserve">за відмови показується причина; чи розкривати пороги скорингу — уточнити</t>
+    <t xml:space="preserve">за відмови показується причина; чи розкривати пороги скорингу - уточнити</t>
   </si>
   <si>
     <t xml:space="preserve">О-4 (похідна)</t>
@@ -235,7 +235,7 @@
     <t xml:space="preserve">не телефонувати у відділення</t>
   </si>
   <si>
-    <t xml:space="preserve">статуси: подано, ручний розгляд, схвалено, відмовлено, не підтверджено; для клієнта без заявок — повідомлення, а не порожній екран</t>
+    <t xml:space="preserve">статуси: подано, ручний розгляд, схвалено, відмовлено, не підтверджено; для клієнта без заявок - повідомлення, а не порожній екран</t>
   </si>
   <si>
     <t xml:space="preserve">О-6 (пряма)</t>
@@ -268,7 +268,7 @@
     <t xml:space="preserve">отримати кошти без візиту у відділення</t>
   </si>
   <si>
-    <t xml:space="preserve">підтвердження доступне лише у статусі «схвалено»; без підтвердження за 7 днів — статус «не підтверджено»</t>
+    <t xml:space="preserve">підтвердження доступне лише у статусі «схвалено»; без підтвердження за 7 днів - статус «не підтверджено»</t>
   </si>
   <si>
     <t xml:space="preserve">О-6 (похідна)</t>
@@ -328,7 +328,7 @@
     <t xml:space="preserve">О-5 (похідна)</t>
   </si>
   <si>
-    <t xml:space="preserve">Рішення ризик-менеджера існує і в поточному продукті (процес 3, крок 4) — нова функція лише додає онлайн-джерело заявок</t>
+    <t xml:space="preserve">Рішення ризик-менеджера існує і в поточному продукті (процес 3, крок 4) - нова функція лише додає онлайн-джерело заявок</t>
   </si>
   <si>
     <t xml:space="preserve">US-16</t>
@@ -397,10 +397,10 @@
     <t xml:space="preserve">подати повну заявку, не вводячи параметри розрахунку вдруге</t>
   </si>
   <si>
-    <t xml:space="preserve">тіло кредиту = сума − перший внесок; перший внесок 0, дорівнює сумі, більший за суму; рахунок обирається зі списку власних рахунків клієнта; параметри з калькулятора переносяться без змін</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Процес 3, крок 1 вимагає першого внеску і рахунку, яких калькулятор (О-1) не містить — без них заявка з калькулятора неповна. Остаточне формулювання залежить від рішення за В6</t>
+    <t xml:space="preserve">тіло кредиту = сума - перший внесок; перший внесок 0, дорівнює сумі, більший за суму; рахунок обирається зі списку власних рахунків клієнта; параметри з калькулятора переносяться без змін</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Процес 3, крок 1 вимагає першого внеску і рахунку, яких калькулятор (О-1) не містить - без них заявка з калькулятора неповна. Остаточне формулювання залежить від рішення за В6</t>
   </si>
   <si>
     <t xml:space="preserve">Таблиця 2. Очікування замовника (каталог, розділ 4.4)</t>
@@ -478,7 +478,7 @@
     <t xml:space="preserve">Прозорий статус без дзвінків у відділення</t>
   </si>
   <si>
-    <t xml:space="preserve">Рамка замовлення (4.4): умови кредиту мають бути відомі клієнту до візиту у відділення; ліміти й формули — збігатися з банківськими, без приблизних цифр.</t>
+    <t xml:space="preserve">Рамка замовлення (4.4): умови кредиту мають бути відомі клієнту до візиту у відділення; ліміти й формули - збігатися з банківськими, без приблизних цифр.</t>
   </si>
   <si>
     <t xml:space="preserve">Таблиця 3. Трасування «очікування → user stories»</t>
@@ -502,373 +502,376 @@
     <t xml:space="preserve">US-01, US-02</t>
   </si>
   <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">так</t>
+  </si>
+  <si>
+    <t xml:space="preserve">графік за місяцями</t>
+  </si>
+  <si>
+    <t xml:space="preserve">валідація лімітів із поясненням</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-04, US-05, US-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-16, US-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">заявка з калькулятора + попереднє рішення</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-07, US-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-09, US-18, US-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">черга ручного розгляду зі скорингом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-13, US-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">статус заявки + повідомлення</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-10, US-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пряма - очікування названо текстом у 4.4. Похідна - story виведена командою з ролей і процесів легенди. 6 очікувань → 19 stories: 12 прямих, 7 похідних; кожне очікування має щонайменше одну пряму story.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Таблиця 4. Що нова функція змінює для кожної ролі (каталог, розділ 4.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Роль</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Що робить зараз</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Що змінює нова функція</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подає заявку на кредит, вказуючи суму, перший внесок і рахунок; умови дізнається у відділенні</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рахує платіж сам, бачить графік і межі, подає заявку з калькулятора, стежить за статусом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-01…US-12, US-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Розглядає заявки, що не пройшли автоматичний скоринг, встановлює ліміти</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отримує заявки з онлайн-джерела разом із результатом скорингу і параметрами клієнта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-13, US-14, US-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Керує параметрами лімітів і тарифів, журналом аудиту</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отримує нові параметри під керування - межі суми, строку і ставки калькулятора</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Перевіряє документи клієнтів, супроводжує відкриття рахунків, розбирає спірні операції</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бачить, що заявка надійшла з калькулятора, і не перепитує вже введені дані</t>
+  </si>
+  <si>
+    <t xml:space="preserve">У demo ParaBank ролі операціоніста, ризик-менеджера й адміністратора не представлені (каталог 4.5, «Обмеження»): це внутрішні ролі для BPMN і user stories; тест-кейсів спринта 3 на них не буде.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Таблиця 5. Модель 1 «Відкриття рахунку» — елементи. Пули: «Клієнт»; «ФінКит» (доріжки «Система», «Операціоніст»)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">№</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пул / доріжка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тип елемента</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Назва й опис</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Початкова подія (проста)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Виникла потреба у новому рахунку»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Задача</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Обрати тип рахунку (поточний / ощадний)»; асоціація до об'єкта даних «Заявка на рахунок»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Обрати рахунок для початкового внеску»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Задача + кидальна подія-повідомлення</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Надіслати заявку на відкриття» - потік повідомлень до 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шлюз XOR за подіями</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Отримано номер рахунку» → 6; «Отримано відмову» → 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кінцева подія</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Рахунок відкрито»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«У відкритті відмовлено»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ФінКит / Система</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Початкова подія-повідомлення</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Отримано заявку на відкриття» (ловить повідомлення з 4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шлюз XOR за даними</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Клієнт ідентифікований?» - «ні» → 10; «так» → 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ФінКит / Операціоніст</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Згорнутий підпроцес</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Перевірити документи клієнта» - окрема діаграма, у норматив моделей не входить</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Документи підтверджено?» - «ні» → 12; «так» → 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Надіслати відмову за документами» → до 5; далі кінцева подія «Відмовлено (документи)»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Перевірити достатність коштів на рахунку-джерелі»; асоціація до сховища даних «Реєстр рахунків»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Коштів достатньо?» - «ні» → 15; «так» → 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Надіслати відмову за коштами» → до 5; далі кінцева подія «Недостатньо коштів»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Створити рахунок і перенести початковий внесок»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Надіслати номер нового рахунку» → до 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Текстова анотація</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Мінімальний внесок для відкриття - за розділом BL; у demo уточнюється на місці» (до 13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Три кінцеві події банку = три результати легенди: рахунок відкрито / відмовлено за документами / недостатньо коштів.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Таблиця 6. Модель 2 «Переказ коштів» — елементи. Пули: «Клієнт»; «ФінКит» (доріжки «Система», «Операціоніст»); «Процесинговий центр»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Потрібно переказати кошти»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Ввести суму і рахунки відправника й одержувача»; асоціація до об'єкта даних «Переказ»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Надіслати форму переказу» - потік повідомлень до 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Отримано підтвердження» → 5; «Отримано відмову» → 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Переказ виконано»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Переказ не виконано»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Отримано форму переказу»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Перевірити формат реквізитів (IBAN, сума)»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Реквізити коректні?» - «ні» → 18; «так» → 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Перевірити баланс і денний ліміт»; асоціація до сховища «Реєстр рахунків»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Ліміт перевищено?» - «так» → 12; «ні» (гілка за замовчуванням) → 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Підтвердити операцію понад ліміт»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Операціоніст підтвердив?» - «ні» → 19; «так» → 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шлюз ТА (розгалуження)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Паралельно 15 і 16 - списання і зарахування однією транзакцією; потік повідомлень до 22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Задача + межова проміжна подія-помилка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Списати кошти з рахунку відправника»; на межі - «Помилка платіжного шлюзу» → 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Зарахувати кошти на рахунок одержувача»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шлюз ТА (синхронізація)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Чекає обидві гілки розгалуження 14 → 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Надіслати відмову системи» → до 4; далі кінцева подія «Відхилено системою»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Надіслати відмову операціоніста» → до 4; далі кінцева подія «Відхилено операціоністом»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Записати обидві операції в історію і повідомити клієнта» → до 4; асоціація до сховища «Журнал транзакцій»; далі кінцева подія «Переказ виконано»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дія-компенсація</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Скасувати списання» - прив'язана до події-помилки на межі 15; далі кінцева подія «Технічна помилка»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Процесинговий центр</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Отримано запит на проведення»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Провести операцію і підтвердити» - потік повідомлень назад у доріжку «Система»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Операцію проведено»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Списання і зарахування - одна транзакція; роздільне виконання спричинило інцидент подвійного списання, після якого створено відділ якості» (до 14)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Розгалуження ТА (14) закривається синхронізуючим ТА (17). Якщо закрити виключним АБО — задача 20 виконається двічі (типова помилка №3 методички).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Таблиця 7. Модель 3 «Оформлення кредиту» — елементи. Пули: «Клієнт»; «ФінКит» (доріжки «Система (скоринг)», «Ризик-менеджер»)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Потрібен кредит»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Вказати суму, перший внесок і рахунок»; асоціація до об'єкта даних «Заявка на кредит»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Подати заявку» - потік повідомлень до 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Проміжна подія-повідомлення (ловить)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Отримано рішення за заявкою»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Рішення позитивне?» - «ні» → 6; «так» → 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Кредит не надано»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Задача + межова проміжна подія-таймер</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Підтвердити умови кредиту»; на межі - «Минуло 7 днів» → 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Умови не підтверджено»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Кредит отримано»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Отримано заявку на кредит»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Перевірити межі суми і строку»; асоціація до анотації 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Параметри в межах?» - «ні» → 17; «так» → 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Розгорнутий підпроцес</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Скоринг заявки» — внутрішні кроки: перевірка доходу, кредитної історії, наявного ліміту</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шлюз XOR за даними (три гілки)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Результат скорингу?» - «відмова» → 17; «гранична оцінка або велика сума» → 15; «схвалено» → 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ФінКит / Ризик-менеджер</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Розглянути заявку вручну»; асоціація до об'єкта даних «Заявка на кредит»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Рішення ризик-менеджера?» - «відхилено» → кінцева подія «Відмовлено ризик-менеджером»; «схвалено» → 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Повідомити автоматичну відмову» → до 4; далі кінцева подія «Відмовлено автоматично»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Повідомити схвалення й умови» → до 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Отримано підтвердження умов» → 21; «Минуло 7 днів» (таймер) → кінцева подія «Не підтверджено»</t>
+  </si>
+  <si>
     <t xml:space="preserve">—</t>
   </si>
   <si>
-    <t xml:space="preserve">так</t>
-  </si>
-  <si>
-    <t xml:space="preserve">графік за місяцями</t>
-  </si>
-  <si>
-    <t xml:space="preserve">валідація лімітів із поясненням</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-04, US-05, US-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-16, US-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">заявка з калькулятора + попереднє рішення</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-07, US-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-09, US-18, US-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">черга ручного розгляду зі скорингом</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-13, US-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">статус заявки + повідомлення</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-10, US-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Пряма — очікування названо текстом у 4.4. Похідна — story виведена командою з ролей і процесів легенди. 6 очікувань → 19 stories: 12 прямих, 7 похідних; кожне очікування має щонайменше одну пряму story.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Таблиця 4. Що нова функція змінює для кожної ролі (каталог, розділ 4.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Роль</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Що робить зараз</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Що змінює нова функція</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stories</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Подає заявку на кредит, вказуючи суму, перший внесок і рахунок; умови дізнається у відділенні</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Рахує платіж сам, бачить графік і межі, подає заявку з калькулятора, стежить за статусом</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-01…US-12, US-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Розглядає заявки, що не пройшли автоматичний скоринг, встановлює ліміти</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Отримує заявки з онлайн-джерела разом із результатом скорингу і параметрами клієнта</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-13, US-14, US-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Керує параметрами лімітів і тарифів, журналом аудиту</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Отримує нові параметри під керування — межі суми, строку і ставки калькулятора</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Перевіряє документи клієнтів, супроводжує відкриття рахунків, розбирає спірні операції</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Бачить, що заявка надійшла з калькулятора, і не перепитує вже введені дані</t>
-  </si>
-  <si>
-    <t xml:space="preserve">У demo ParaBank ролі операціоніста, ризик-менеджера й адміністратора не представлені (каталог 4.5, «Обмеження»): це внутрішні ролі для BPMN і user stories; тест-кейсів спринта 3 на них не буде.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Таблиця 5. Модель 1 «Відкриття рахунку» — елементи. Пули: «Клієнт»; «ФінКит» (доріжки «Система», «Операціоніст»)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">№</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Пул / доріжка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тип елемента</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Назва й опис</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Початкова подія (проста)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Виникла потреба у новому рахунку»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Задача</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Обрати тип рахунку (поточний / ощадний)»; асоціація до об'єкта даних «Заявка на рахунок»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Обрати рахунок для початкового внеску»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Задача + кидальна подія-повідомлення</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Надіслати заявку на відкриття» — потік повідомлень до 8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Шлюз XOR за подіями</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Отримано номер рахунку» → 6; «Отримано відмову» → 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кінцева подія</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Рахунок відкрито»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«У відкритті відмовлено»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ФінКит / Система</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Початкова подія-повідомлення</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Отримано заявку на відкриття» (ловить повідомлення з 4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Шлюз XOR за даними</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Клієнт ідентифікований?» — «ні» → 10; «так» → 13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ФінКит / Операціоніст</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Згорнутий підпроцес</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Перевірити документи клієнта» — окрема діаграма, у норматив моделей не входить</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Документи підтверджено?» — «ні» → 12; «так» → 13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Надіслати відмову за документами» → до 5; далі кінцева подія «Відмовлено (документи)»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Перевірити достатність коштів на рахунку-джерелі»; асоціація до сховища даних «Реєстр рахунків»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Коштів достатньо?» — «ні» → 15; «так» → 16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Надіслати відмову за коштами» → до 5; далі кінцева подія «Недостатньо коштів»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Створити рахунок і перенести початковий внесок»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Надіслати номер нового рахунку» → до 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Текстова анотація</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Мінімальний внесок для відкриття — за розділом BL; у demo уточнюється на місці» (до 13)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Три кінцеві події банку = три результати легенди: рахунок відкрито / відмовлено за документами / недостатньо коштів.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Таблиця 6. Модель 2 «Переказ коштів» — елементи. Пули: «Клієнт»; «ФінКит» (доріжки «Система», «Операціоніст»); «Процесинговий центр»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Потрібно переказати кошти»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Ввести суму і рахунки відправника й одержувача»; асоціація до об'єкта даних «Переказ»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Надіслати форму переказу» — потік повідомлень до 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Отримано підтвердження» → 5; «Отримано відмову» → 6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Переказ виконано»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Переказ не виконано»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Отримано форму переказу»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Перевірити формат реквізитів (IBAN, сума)»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Реквізити коректні?» — «ні» → 18; «так» → 10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Перевірити баланс і денний ліміт»; асоціація до сховища «Реєстр рахунків»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Ліміт перевищено?» — «так» → 12; «ні» (гілка за замовчуванням) → 14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Підтвердити операцію понад ліміт»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Операціоніст підтвердив?» — «ні» → 19; «так» → 14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Шлюз ТА (розгалуження)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Паралельно 15 і 16 — списання і зарахування однією транзакцією; потік повідомлень до 22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Задача + межова проміжна подія-помилка</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Списати кошти з рахунку відправника»; на межі — «Помилка платіжного шлюзу» → 21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Зарахувати кошти на рахунок одержувача»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Шлюз ТА (синхронізація)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Чекає обидві гілки розгалуження 14 → 20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Надіслати відмову системи» → до 4; далі кінцева подія «Відхилено системою»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Надіслати відмову операціоніста» → до 4; далі кінцева подія «Відхилено операціоністом»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Записати обидві операції в історію і повідомити клієнта» → до 4; асоціація до сховища «Журнал транзакцій»; далі кінцева подія «Переказ виконано»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Дія-компенсація</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Скасувати списання» — прив'язана до події-помилки на межі 15; далі кінцева подія «Технічна помилка»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Процесинговий центр</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Отримано запит на проведення»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Провести операцію і підтвердити» — потік повідомлень назад у доріжку «Система»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Операцію проведено»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Списання і зарахування — одна транзакція; роздільне виконання спричинило інцидент подвійного списання, після якого створено відділ якості» (до 14)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Розгалуження ТА (14) закривається синхронізуючим ТА (17). Якщо закрити виключним АБО — задача 20 виконається двічі (типова помилка №3 методички).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Таблиця 7. Модель 3 «Оформлення кредиту» — елементи. Пули: «Клієнт»; «ФінКит» (доріжки «Система (скоринг)», «Ризик-менеджер»)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Потрібен кредит»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Вказати суму, перший внесок і рахунок»; асоціація до об'єкта даних «Заявка на кредит»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Подати заявку» — потік повідомлень до 10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Проміжна подія-повідомлення (ловить)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Отримано рішення за заявкою»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Рішення позитивне?» — «ні» → 6; «так» → 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Кредит не надано»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Задача + межова проміжна подія-таймер</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Підтвердити умови кредиту»; на межі — «Минуло 7 днів» → 8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Умови не підтверджено»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Кредит отримано»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Отримано заявку на кредит»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Перевірити межі суми і строку»; асоціація до анотації 20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Параметри в межах?» — «ні» → 17; «так» → 13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Розгорнутий підпроцес</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Скоринг заявки» — внутрішні кроки: перевірка доходу, кредитної історії, наявного ліміту</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Шлюз XOR за даними (три гілки)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Результат скорингу?» — «відмова» → 17; «гранична оцінка або велика сума» → 15; «схвалено» → 18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ФінКит / Ризик-менеджер</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Розглянути заявку вручну»; асоціація до об'єкта даних «Заявка на кредит»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Рішення ризик-менеджера?» — «відхилено» → кінцева подія «Відмовлено ризик-менеджером»; «схвалено» → 18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Повідомити автоматичну відмову» → до 4; далі кінцева подія «Відмовлено автоматично»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Повідомити схвалення й умови» → до 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Отримано підтвердження умов» → 21; «Минуло 7 днів» (таймер) → кінцева подія «Не підтверджено»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Ліміти суми, строку і ставки — за розділом BL специфікації» (до 11)</t>
+    <t xml:space="preserve">«Ліміти суми, строку і ставки - за розділом BL специфікації» (до 11)</t>
   </si>
   <si>
     <t xml:space="preserve">«Зарахувати кошти і створити графік платежів»; асоціація до об'єкта даних «Графік платежів»</t>
@@ -877,7 +880,7 @@
     <t xml:space="preserve">«Кредит видано»</t>
   </si>
   <si>
-    <t xml:space="preserve">«Онлайн-калькулятор, подання заявки з калькулятора і статус у кабінеті — замовлення на нову функцію (О-1…О-6); у поточній версії продукту відсутні» (до 2)</t>
+    <t xml:space="preserve">«Онлайн-калькулятор, подання заявки з калькулятора і статус у кабінеті - замовлення на нову функцію (О-1…О-6); у поточній версії продукту відсутні» (до 2)</t>
   </si>
   <si>
     <t xml:space="preserve">Анотація 23 обов'язкова: показує, що команда свідомо змоделювала продукт «як є», а нову функцію винесла в беклог (типова помилка №4 методички).</t>
@@ -892,7 +895,7 @@
     <t xml:space="preserve">«Ввести одержувача (назва, адреса, телефон, рахунок) і суму»; асоціація до об'єкта даних «Платіжне доручення»</t>
   </si>
   <si>
-    <t xml:space="preserve">«Надіслати рахунок на оплату» — потік повідомлень до 7</t>
+    <t xml:space="preserve">«Надіслати рахунок на оплату» - потік повідомлень до 7</t>
   </si>
   <si>
     <t xml:space="preserve">«Отримано підтвердження оплати» → 5; «Отримано повідомлення про помилку» → 6</t>
@@ -910,7 +913,7 @@
     <t xml:space="preserve">«Перевірити повноту і формат полів»</t>
   </si>
   <si>
-    <t xml:space="preserve">«Поля коректні?» — «ні» → 10; «так» → 11</t>
+    <t xml:space="preserve">«Поля коректні?» - «ні» → 10; «так» → 11</t>
   </si>
   <si>
     <t xml:space="preserve">«Повідомити помилку у реквізитах» → до 4; далі кінцева подія «Помилка у реквізитах»</t>
@@ -919,7 +922,7 @@
     <t xml:space="preserve">«Перевірити баланс рахунку»; асоціація до сховища «Реєстр рахунків»</t>
   </si>
   <si>
-    <t xml:space="preserve">«Коштів достатньо?» — «ні» → 13; «так» → 14</t>
+    <t xml:space="preserve">«Коштів достатньо?» - «ні» → 13; «так» → 14</t>
   </si>
   <si>
     <t xml:space="preserve">«Повідомити про недостатність коштів» → до 4; далі кінцева подія «Недостатньо коштів»</t>
@@ -928,7 +931,7 @@
     <t xml:space="preserve">«Списати кошти і сформувати платіжне доручення»</t>
   </si>
   <si>
-    <t xml:space="preserve">«Надіслати доручення одержувачу» — потік повідомлень до 18</t>
+    <t xml:space="preserve">«Надіслати доручення одержувачу» - потік повідомлень до 18</t>
   </si>
   <si>
     <t xml:space="preserve">«Показати підтвердження і записати в історію» → до 4; асоціація до сховища «Журнал транзакцій»</t>
@@ -964,7 +967,7 @@
     <t xml:space="preserve">4 моделі (команда з 5 осіб)</t>
   </si>
   <si>
-    <t xml:space="preserve">Моделі 1–4 — усі чотири процеси легенди (каталог 4.3)</t>
+    <t xml:space="preserve">Моделі 1-4 - усі чотири процеси легенди (каталог 4.3)</t>
   </si>
   <si>
     <t xml:space="preserve">≥3 різні типи шлюзів</t>
@@ -982,7 +985,7 @@
     <t xml:space="preserve">Три види подій</t>
   </si>
   <si>
-    <t xml:space="preserve">Початкові — всі моделі; проміжні: повідомлення (М3 №4), таймер (М3 №7, №19), помилка на межі (М2 №15); кінцеві — всі моделі</t>
+    <t xml:space="preserve">Початкові - всі моделі; проміжні: повідомлення (М3 №4), таймер (М3 №7, №19), помилка на межі (М2 №15); кінцеві - всі моделі</t>
   </si>
   <si>
     <t xml:space="preserve">Потоки повідомлень між пулами</t>
@@ -1006,7 +1009,7 @@
     <t xml:space="preserve">Кожна доріжка має ≥1 дію</t>
   </si>
   <si>
-    <t xml:space="preserve">«Операціоніст» — М1 №10–11, М2 №12–13; «Ризик-менеджер» — М3 №15–16; «Система» — усі моделі</t>
+    <t xml:space="preserve">«Операціоніст» - М1 №10–11, М2 №12–13; «Ризик-менеджер» - М3 №15–16; «Система» - усі моделі</t>
   </si>
   <si>
     <t xml:space="preserve">User stories ≥15</t>
@@ -1045,10 +1048,10 @@
     <t xml:space="preserve">В1</t>
   </si>
   <si>
-    <t xml:space="preserve">Заглушки у примітках: US-04, US-05, US-06 — межі суми, строку, ставки (SRS, розділ BL); US-08 — час відповіді (SRS, розділ P-); US-01 — контрольний приклад орієнтовний</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Підставити значення з SRS_02_ФінКит.html: межі — з розділу BL, час відповіді — з розділу P-. Перевірити, що контрольний приклад US-01 потрапляє в межі BL, інакше замінити числа. Якщо межі в SRS відсутні — заглушку замінити на «межа в SRS відсутня — кандидат у реєстр дефектів вимог (критерій повноти, спринт 2)»</t>
+    <t xml:space="preserve">Заглушки у примітках: US-04, US-05, US-06 - межі суми, строку, ставки (SRS, розділ BL); US-08 - час відповіді (SRS, розділ P-); US-01 - контрольний приклад орієнтовний</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Підставити значення з SRS_02_ФінКит.html: межі - з розділу BL, час відповіді - з розділу P-. Перевірити, що контрольний приклад US-01 потрапляє в межі BL, інакше замінити числа. Якщо межі в SRS відсутні - заглушку замінити на «межа в SRS відсутня - кандидат у реєстр дефектів вимог (критерій повноти, спринт 2)»</t>
   </si>
   <si>
     <t xml:space="preserve">Тест-аналітик, до дня 7</t>
@@ -1057,7 +1060,7 @@
     <t xml:space="preserve">В2</t>
   </si>
   <si>
-    <t xml:space="preserve">Пріоритети US-02 (переплата, О-1) і US-03 (графік, О-2): обидві — прямі складові очікувань, але стоять Medium, тоді як решта прямих stories — High</t>
+    <t xml:space="preserve">Пріоритети US-02 (переплата, О-1) і US-03 (графік, О-2): обидві - прямі складові очікувань, але стоять Medium, тоді як решта прямих stories — High</t>
   </si>
   <si>
     <t xml:space="preserve">Рішення однакове для обох: або підняти до High, або лишити Medium з обґрунтуванням із колонки I. Відповідь Тест-аналітика і Керівника тестування на демо має збігатися</t>
@@ -1087,7 +1090,7 @@
     <t xml:space="preserve">В5</t>
   </si>
   <si>
-    <t xml:space="preserve">Колонка «Статус»: усі 19 рядків — «чернетка»</t>
+    <t xml:space="preserve">Колонка «Статус»: усі 19 рядків - «чернетка»</t>
   </si>
   <si>
     <t xml:space="preserve">Після рецензії: без зауважень → «затверджено»; із прийнятим зауваженням → лишається «чернетка» до виправлення; свідома відмова → «відхилено», рядок не видаляється</t>
@@ -1099,13 +1102,13 @@
     <t xml:space="preserve">В6</t>
   </si>
   <si>
-    <t xml:space="preserve">Перший внесок і рахунок зарахування відсутні у калькуляторі (О-1), але обов'язкові для заявки (процес 3, крок 1) — заявка з калькулятора (О-4) виходить неповною</t>
+    <t xml:space="preserve">Перший внесок і рахунок зарахування відсутні у калькуляторі (О-1), але обов'язкові для заявки (процес 3, крок 1) - заявка з калькулятора (О-4) виходить неповною</t>
   </si>
   <si>
     <t xml:space="preserve">Уточнити в замовника: перший внесок стає входом калькулятора (змінює P у US-01) чи додається на кроці подання (US-19). До відповіді US-19 лишається чернеткою</t>
   </si>
   <si>
-    <t xml:space="preserve">КТ → замовник; питання — у docs/sprint1/audit.md (АО)</t>
+    <t xml:space="preserve">КТ → замовник; питання - у docs/sprint1/audit.md (АО)</t>
   </si>
   <si>
     <t xml:space="preserve">Зведення за статусами (формули рахують колонку G таблиці 1)</t>
@@ -1241,48 +1244,44 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1366,34 +1365,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1539,7 +1538,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I47"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
@@ -1558,587 +1557,587 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="B4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="7" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="B5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="B6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="B7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="B8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="7" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="B9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="7" t="s">
+      <c r="B10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="7" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="7" t="s">
+      <c r="B11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="7" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="7" t="s">
+      <c r="B12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="7" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="7" t="s">
+      <c r="B13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="7" t="s">
+      <c r="B14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="I14" s="8" t="s">
+      <c r="I14" s="7" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="7" t="s">
+      <c r="B15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="7" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="I16" s="7" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="I17" s="7" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="I18" s="7" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="I19" s="7" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="I20" s="8" t="s">
+      <c r="I20" s="7" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="7" t="s">
+      <c r="B22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="I22" s="7" t="s">
         <v>123</v>
       </c>
     </row>
@@ -2174,170 +2173,170 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>336</v>
       </c>
+      <c r="E3" s="4" t="s">
+        <v>337</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="B4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="D4" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="E4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="B5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="E5" s="8"/>
+      <c r="D5" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="E5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="B6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="E6" s="8"/>
+      <c r="D6" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="E6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="B8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="D8" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="E8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="B9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="D9" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="E9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
-        <v>360</v>
-      </c>
-      <c r="B12" s="10" t="n">
+      <c r="A12" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="B12" s="9" t="n">
         <f aca="false">COUNTA('Спринт 1'!A4:A22)</f>
         <v>19</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="9" t="n">
         <f aca="false">COUNTIF('Спринт 1'!G4:G22,"чернетка")</f>
         <v>19</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>361</v>
-      </c>
-      <c r="B14" s="10" t="n">
+      <c r="A14" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="B14" s="9" t="n">
         <f aca="false">COUNTIF('Спринт 1'!G4:G22,"затверджено")</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
-        <v>362</v>
-      </c>
-      <c r="B15" s="10" t="n">
+      <c r="A15" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="B15" s="9" t="n">
         <f aca="false">COUNTIF('Спринт 1'!G4:G22,"відхилено")</f>
         <v>0</v>
       </c>
@@ -2359,7 +2358,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52"/>
@@ -2373,110 +2372,110 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="247.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="8" t="s">
         <v>149</v>
       </c>
     </row>
@@ -2497,7 +2496,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
@@ -2512,131 +2511,131 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="7" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="7" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="281.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="8" t="s">
         <v>170</v>
       </c>
     </row>
@@ -2657,7 +2656,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="44"/>
@@ -2670,82 +2669,82 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="8" t="s">
+      <c r="A4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="8" t="s">
         <v>186</v>
       </c>
     </row>
@@ -2766,7 +2765,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
@@ -2780,292 +2779,292 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="B6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="B10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="8" t="s">
+      <c r="A15" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="7" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="7" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="281.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="8" t="s">
         <v>221</v>
       </c>
     </row>
@@ -3086,7 +3085,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
@@ -3100,376 +3099,376 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="B6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="8" t="s">
+      <c r="A15" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="7" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="7" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="7" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="7" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="n">
+      <c r="A25" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="7" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="7" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="n">
+      <c r="A27" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="7" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="n">
+      <c r="A28" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="7" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="348" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="8" t="s">
         <v>253</v>
       </c>
     </row>
@@ -3490,7 +3489,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
@@ -3504,349 +3503,349 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="B6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="7" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="B10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="B11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="B12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="n">
+      <c r="A13" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="8" t="s">
+      <c r="A15" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="n">
+      <c r="A17" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="n">
+      <c r="A19" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="7" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="n">
+      <c r="A21" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="7" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="n">
+      <c r="A23" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C23" s="8" t="s">
+      <c r="B23" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="7" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="D26" s="8" t="s">
-        <v>282</v>
+      <c r="D26" s="7" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="359.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9" t="s">
-        <v>283</v>
+      <c r="A28" s="8" t="s">
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -3866,7 +3865,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
@@ -3876,325 +3875,325 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="n">
+      <c r="A4" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>285</v>
+      <c r="D4" s="7" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>286</v>
+      <c r="D5" s="7" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="B6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>287</v>
+      <c r="D6" s="7" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="n">
+      <c r="A7" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>288</v>
+      <c r="D7" s="7" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="8" t="s">
+      <c r="B8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>289</v>
+      <c r="D8" s="7" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="n">
+      <c r="A9" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="B9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>290</v>
+      <c r="D9" s="7" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>291</v>
+      <c r="D10" s="7" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="n">
+      <c r="A11" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C14" s="8" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C20" s="8" t="s">
+      <c r="D22" s="7" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>304</v>
+      <c r="D23" s="7" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C24" s="8" t="s">
+      <c r="B24" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="D24" s="8" t="s">
-        <v>305</v>
+      <c r="D24" s="7" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="258.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="s">
-        <v>306</v>
+      <c r="A26" s="8" t="s">
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -4214,7 +4213,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="90"/>
@@ -4222,108 +4221,108 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>309</v>
       </c>
+      <c r="B3" s="4" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="B4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>311</v>
       </c>
+      <c r="B4" s="7" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="B5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>313</v>
       </c>
+      <c r="B5" s="7" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="B6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>315</v>
       </c>
+      <c r="B6" s="7" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="B7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>317</v>
       </c>
+      <c r="B7" s="7" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="B8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>319</v>
       </c>
+      <c r="B8" s="7" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="B9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>321</v>
       </c>
+      <c r="B9" s="7" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="B10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>323</v>
       </c>
+      <c r="B10" s="7" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="B11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>325</v>
       </c>
+      <c r="B11" s="7" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
-        <v>326</v>
-      </c>
-      <c r="B12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>327</v>
       </c>
+      <c r="B12" s="7" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="B13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>329</v>
       </c>
+      <c r="B13" s="7" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="B14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>331</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>332</v>
       </c>
     </row>
   </sheetData>

--- a/docs/sprint1/backlog.xlsx
+++ b/docs/sprint1/backlog.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -19,6 +19,9 @@
     <sheet name="Покриття нотації" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="Відкриті питання" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Спринт 1'!$A$3:$I$22</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -29,12 +32,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="350">
   <si>
     <t xml:space="preserve">Таблиця 1. Беклог вимог (user stories)</t>
   </si>
   <si>
-    <t xml:space="preserve">Продукт: П2 «ФінКит» (finkit) · Спринт 1 · Команда: &lt;назва&gt; · Дата: &lt;дд.мм.2026&gt; · Автор: &lt;ПІБ&gt;, Тест-аналітик · Рецензент: &lt;ПІБ&gt;, &lt;дата&gt;</t>
+    <t xml:space="preserve">Продукт: П2 «ФінКит» (finkit) · Спринт 1 · Команда: ____ · Автор: ____ (Тест-аналітик) · Дата: ____ · Рецензент: ____</t>
   </si>
   <si>
     <t xml:space="preserve">ID</t>
@@ -79,7 +82,7 @@
     <t xml:space="preserve">High</t>
   </si>
   <si>
-    <t xml:space="preserve">A = P·i / (1 − (1+i)^−n), i = річна ставка / 12 / 100; округлення до 0,01 HALF_UP; контрольний приклад (орієнтовний, до підстановки меж BL - див. В1): P = 100 000, 20 % річних, n = 12 → A = 9 263,45, переплата = 11 161,40</t>
+    <t xml:space="preserve">BL-10: A = P·i / (1 − (1+i)^−n), i = r / 12 / 100; BigDecimal, HALF_UP до копійки, проміжні обчислення не округлюються; контроль: P = 100 000, r = 20, n = 12 → A = 9 263,45</t>
   </si>
   <si>
     <t xml:space="preserve">чернетка</t>
@@ -103,7 +106,7 @@
     <t xml:space="preserve">Medium</t>
   </si>
   <si>
-    <t xml:space="preserve">переплата = A·n − P; більший строк за незмінних суми і ставки дає більшу переплату</t>
+    <t xml:space="preserve">BL-20: переплата = A·n − P, де A — округлений результат BL-10; контроль: 9 263,45 · 12 − 100 000 = 11 161,40; більший строк за незмінних суми і ставки дає більшу переплату</t>
   </si>
   <si>
     <t xml:space="preserve">Виводиться з розрахунку US-01; калькулятор корисний і без окремого показника переплати</t>
@@ -124,7 +127,7 @@
     <t xml:space="preserve">О-2 (пряма)</t>
   </si>
   <si>
-    <t xml:space="preserve">Окреме очікування замовника, але рішення клієнт ухвалює вже за платежем з US-01 — див. «Відкриті питання», В2</t>
+    <t xml:space="preserve">Окреме очікування замовника, але рішення клієнт ухвалює вже за платежем з US-01 — див. «Відкриті питання», В1</t>
   </si>
   <si>
     <t xml:space="preserve">US-04</t>
@@ -136,7 +139,7 @@
     <t xml:space="preserve">виправити введення до подання заявки</t>
   </si>
   <si>
-    <t xml:space="preserve">межі суми &lt;межі з SRS, розділ BL&gt;: min−0,01 / min / max / max+0,01; порожнє, 0, від'ємне, нечислове; повідомлення називає саме суму</t>
+    <t xml:space="preserve">BL-30: сума 1 000..1 000 000 грн включно; 999 / 1 000 / 1 000 000 / 1 000 001; порожнє, 0, від’ємне, нечислове; поза межами — IllegalArgumentException, повідомлення називає саме суму (F-110 називає мінімум 500 грн — розбіжність у SRS)</t>
   </si>
   <si>
     <t xml:space="preserve">О-3 (пряма)</t>
@@ -154,7 +157,7 @@
     <t xml:space="preserve">не подавати заявку, яку банк відхилить</t>
   </si>
   <si>
-    <t xml:space="preserve">межі строку &lt;межі з SRS, розділ BL&gt;: min−1 / min / max / max+1; 0, від'ємне, дробове; повідомлення називає саме строк</t>
+    <t xml:space="preserve">BL-30: строк 3..60 місяців включно; 2 / 3 / 60 / 61; 0, від’ємне, дробове; поза межами — IllegalArgumentException, повідомлення називає саме строк</t>
   </si>
   <si>
     <t xml:space="preserve">Те саме для строку: неправильний строк змінює і платіж, і графік</t>
@@ -169,7 +172,7 @@
     <t xml:space="preserve">бачити реальні умови банку</t>
   </si>
   <si>
-    <t xml:space="preserve">межі ставки &lt;межі з SRS, розділ BL&gt;: межі та 0; за ставки 0 платіж = P/n; повідомлення називає саме ставку</t>
+    <t xml:space="preserve">BL-30: ставка 5..40 % включно; 4 / 5 / 40 / 41; 0 і від’ємна; поза межами — IllegalArgumentException, повідомлення називає саме ставку</t>
   </si>
   <si>
     <t xml:space="preserve">Те саме для ставки; ставка поза межами банку робить весь розрахунок недійсним</t>
@@ -202,7 +205,7 @@
     <t xml:space="preserve">розуміти шанси без очікування дзвінка</t>
   </si>
   <si>
-    <t xml:space="preserve">час відповіді не більший за &lt;значення з SRS, розділ P-&gt;; три результати: схвалено / відмова / ручний розгляд; текст рішення непорожній</t>
+    <t xml:space="preserve">час відображення сторінки — P-10 (0,1 с); три результати: схвалено / відмова / ручний розгляд; текст рішення непорожній</t>
   </si>
   <si>
     <t xml:space="preserve">Попереднє рішення «за кілька секунд» - окремо назване очікування</t>
@@ -337,19 +340,16 @@
     <t xml:space="preserve">Адміністратор</t>
   </si>
   <si>
-    <t xml:space="preserve">налаштовувати межі суми, строку і ставки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">змінювати умови без участі розробників</t>
-  </si>
-  <si>
-    <t xml:space="preserve">змінена межа діє з наступного розрахунку; min більший за max відхиляється; зміна фіксується у журналі аудиту</t>
-  </si>
-  <si>
-    <t xml:space="preserve">О-3 (похідна)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Межі можна перший час тримати в конфігурації; без самообслуговування функція працює</t>
+    <t xml:space="preserve">налаштовувати параметри кредитного рішення: спосіб опрацювання заявки і поріг у відсотках</t>
+  </si>
+  <si>
+    <t xml:space="preserve">змінювати умови схвалення без участі розробників</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3 п. 5: параметри задає адміністратор на сторінці адміністрування; змінений поріг діє з наступної заявки; поріг поза 0..100 % відхиляється; зміна фіксується у журналі аудиту. Межі суми, строку і ставки конфігурації не підлягають — вони фіксовані BL-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">За 2.1 і 2.3 п. 5 адміністратор керує способом опрацювання заявки і порогом, а не межами калькулятора; без самообслуговування функція працює</t>
   </si>
   <si>
     <t xml:space="preserve">US-17</t>
@@ -397,18 +397,15 @@
     <t xml:space="preserve">подати повну заявку, не вводячи параметри розрахунку вдруге</t>
   </si>
   <si>
-    <t xml:space="preserve">тіло кредиту = сума - перший внесок; перший внесок 0, дорівнює сумі, більший за суму; рахунок обирається зі списку власних рахунків клієнта; параметри з калькулятора переносяться без змін</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Процес 3, крок 1 вимагає першого внеску і рахунку, яких калькулятор (О-1) не містить - без них заявка з калькулятора неповна. Остаточне формулювання залежить від рішення за В6</t>
+    <t xml:space="preserve">F-110: сума кредиту, перший внесок і рахунок списання внеску; тіло кредиту = сума − перший внесок; перший внесок 0, дорівнює сумі, більший за суму; рахунок обирається зі списку власних рахунків клієнта; параметри з калькулятора переносяться без змін</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-110 вимагає суми, першого внеску і рахунку списання, яких калькулятор (BL-10) не приймає — без них заявка з калькулятора неповна</t>
   </si>
   <si>
     <t xml:space="preserve">Таблиця 2. Очікування замовника (каталог, розділ 4.4)</t>
   </si>
   <si>
-    <t xml:space="preserve">Продукт: П2 «ФінКит» · Спринт 1 · Команда: &lt;назва&gt; · Автор: &lt;ПІБ&gt;, Тест-аналітик · Дата: &lt;дд.мм.2026&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">Очікування замовника (дослівно)</t>
   </si>
   <si>
@@ -517,72 +514,75 @@
     <t xml:space="preserve">US-04, US-05, US-06</t>
   </si>
   <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">заявка з калькулятора + попереднє рішення</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-07, US-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-09, US-16, US-17, US-18, US-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">черга ручного розгляду зі скорингом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-13, US-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">статус заявки + повідомлення</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-10, US-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пряма — очікування названо текстом у 4.4. Похідна — story виведена з ролей і процесів легенди. 19 stories: 12 прямих, 7 похідних.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Таблиця 4. Що нова функція змінює для кожної ролі (каталог, розділ 4.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Роль</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Що робить зараз</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Що змінює нова функція</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подає заявку на кредит, вказуючи суму, перший внесок і рахунок; умови дізнається у відділенні</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рахує платіж сам, бачить графік і межі, подає заявку з калькулятора, стежить за статусом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-01…US-12, US-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Розглядає заявки, що не пройшли автоматичний скоринг, встановлює ліміти</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отримує заявки з онлайн-джерела разом із результатом скорингу і параметрами клієнта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US-13, US-14, US-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Керує параметрами лімітів і тарифів, журналом аудиту</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отримує під керування параметри кредитного рішення — спосіб опрацювання заявки і поріг у відсотках (2.3 п. 5)</t>
+  </si>
+  <si>
     <t xml:space="preserve">US-16, US-17</t>
   </si>
   <si>
-    <t xml:space="preserve">заявка з калькулятора + попереднє рішення</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-07, US-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-09, US-18, US-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">черга ручного розгляду зі скорингом</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-13, US-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">статус заявки + повідомлення</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-10, US-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Пряма - очікування названо текстом у 4.4. Похідна - story виведена командою з ролей і процесів легенди. 6 очікувань → 19 stories: 12 прямих, 7 похідних; кожне очікування має щонайменше одну пряму story.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Таблиця 4. Що нова функція змінює для кожної ролі (каталог, розділ 4.2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Роль</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Що робить зараз</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Що змінює нова функція</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stories</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Подає заявку на кредит, вказуючи суму, перший внесок і рахунок; умови дізнається у відділенні</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Рахує платіж сам, бачить графік і межі, подає заявку з калькулятора, стежить за статусом</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-01…US-12, US-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Розглядає заявки, що не пройшли автоматичний скоринг, встановлює ліміти</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Отримує заявки з онлайн-джерела разом із результатом скорингу і параметрами клієнта</t>
-  </si>
-  <si>
-    <t xml:space="preserve">US-13, US-14, US-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Керує параметрами лімітів і тарифів, журналом аудиту</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Отримує нові параметри під керування - межі суми, строку і ставки калькулятора</t>
-  </si>
-  <si>
     <t xml:space="preserve">Перевіряє документи клієнтів, супроводжує відкриття рахунків, розбирає спірні операції</t>
   </si>
   <si>
@@ -691,10 +691,7 @@
     <t xml:space="preserve">Текстова анотація</t>
   </si>
   <si>
-    <t xml:space="preserve">«Мінімальний внесок для відкриття - за розділом BL; у demo уточнюється на місці» (до 13)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Три кінцеві події банку = три результати легенди: рахунок відкрито / відмовлено за документами / недостатньо коштів.</t>
+    <t xml:space="preserve">«Початковий внесок при відкритті рахунку — 100 грн (F-60)» (до 13)</t>
   </si>
   <si>
     <t xml:space="preserve">Таблиця 6. Модель 2 «Переказ коштів» — елементи. Пули: «Клієнт»; «ФінКит» (доріжки «Система», «Операціоніст»); «Процесинговий центр»</t>
@@ -790,9 +787,6 @@
     <t xml:space="preserve">«Списання і зарахування - одна транзакція; роздільне виконання спричинило інцидент подвійного списання, після якого створено відділ якості» (до 14)</t>
   </si>
   <si>
-    <t xml:space="preserve">Розгалуження ТА (14) закривається синхронізуючим ТА (17). Якщо закрити виключним АБО — задача 20 виконається двічі (типова помилка №3 методички).</t>
-  </si>
-  <si>
     <t xml:space="preserve">Таблиця 7. Модель 3 «Оформлення кредиту» — елементи. Пули: «Клієнт»; «ФінКит» (доріжки «Система (скоринг)», «Ризик-менеджер»)</t>
   </si>
   <si>
@@ -868,10 +862,7 @@
     <t xml:space="preserve">«Отримано підтвердження умов» → 21; «Минуло 7 днів» (таймер) → кінцева подія «Не підтверджено»</t>
   </si>
   <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«Ліміти суми, строку і ставки - за розділом BL специфікації» (до 11)</t>
+    <t xml:space="preserve">«Сума 1 000..1 000 000 грн, строк 3..60 місяців, ставка 5..40 % (BL-30)» (до 11)</t>
   </si>
   <si>
     <t xml:space="preserve">«Зарахувати кошти і створити графік платежів»; асоціація до об'єкта даних «Графік платежів»</t>
@@ -883,9 +874,6 @@
     <t xml:space="preserve">«Онлайн-калькулятор, подання заявки з калькулятора і статус у кабінеті - замовлення на нову функцію (О-1…О-6); у поточній версії продукту відсутні» (до 2)</t>
   </si>
   <si>
-    <t xml:space="preserve">Анотація 23 обов'язкова: показує, що команда свідомо змоделювала продукт «як є», а нову функцію винесла в беклог (типова помилка №4 методички).</t>
-  </si>
-  <si>
     <t xml:space="preserve">Таблиця 8. Модель 4 «Оплата рахунку» — елементи. Пули: «Клієнт»; «ФінКит» (доріжка «Система»); «Одержувач платежу»</t>
   </si>
   <si>
@@ -952,9 +940,6 @@
     <t xml:space="preserve">«Одержувач платежу у demo не представлений; пул моделює зовнішнього учасника за легендою» (до 18)</t>
   </si>
   <si>
-    <t xml:space="preserve">Усі стрілки, що перетинають межі пулів, — лише пунктирні потоки повідомлень (типова помилка №1 методички).</t>
-  </si>
-  <si>
     <t xml:space="preserve">Таблиця 9. Перевірка набору моделей за Definition of Done спринта 1</t>
   </si>
   <si>
@@ -1048,48 +1033,36 @@
     <t xml:space="preserve">В1</t>
   </si>
   <si>
-    <t xml:space="preserve">Заглушки у примітках: US-04, US-05, US-06 - межі суми, строку, ставки (SRS, розділ BL); US-08 - час відповіді (SRS, розділ P-); US-01 - контрольний приклад орієнтовний</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Підставити значення з SRS_02_ФінКит.html: межі - з розділу BL, час відповіді - з розділу P-. Перевірити, що контрольний приклад US-01 потрапляє в межі BL, інакше замінити числа. Якщо межі в SRS відсутні - заглушку замінити на «межа в SRS відсутня - кандидат у реєстр дефектів вимог (критерій повноти, спринт 2)»</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тест-аналітик, до дня 7</t>
+    <t xml:space="preserve">Пріоритети US-02 (переплата, О-1) і US-03 (графік, О-2): обидві - прямі складові очікувань, але стоять Medium, тоді як решта прямих stories — High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рішення однакове для обох: або підняти до High, або лишити Medium з обґрунтуванням із колонки I. Відповідь Тест-аналітика і Керівника тестування на демо має збігатися</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тест-аналітик + КТ, до рецензії</t>
   </si>
   <si>
     <t xml:space="preserve">В2</t>
   </si>
   <si>
-    <t xml:space="preserve">Пріоритети US-02 (переплата, О-1) і US-03 (графік, О-2): обидві - прямі складові очікувань, але стоять Medium, тоді як решта прямих stories — High</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Рішення однакове для обох: або підняти до High, або лишити Medium з обґрунтуванням із колонки I. Відповідь Тест-аналітика і Керівника тестування на демо має збігатися</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Тест-аналітик + КТ, до рецензії</t>
+    <t xml:space="preserve">US-09: чи розкривати клієнту пороги скорингу у причині відмови</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Винести у перелік очікуваних питань замовника</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аудитор-опонент, docs/sprint1/audit.md</t>
   </si>
   <si>
     <t xml:space="preserve">В3</t>
   </si>
   <si>
-    <t xml:space="preserve">US-09: чи розкривати клієнту пороги скорингу у причині відмови</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Винести у перелік очікуваних питань замовника</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Аудитор-опонент, docs/sprint1/audit.md</t>
+    <t xml:space="preserve">US-15: чи обов'язковий коментар ризик-менеджера до рішення</t>
   </si>
   <si>
     <t xml:space="preserve">В4</t>
   </si>
   <si>
-    <t xml:space="preserve">US-15: чи обов'язковий коментар ризик-менеджера до рішення</t>
-  </si>
-  <si>
-    <t xml:space="preserve">В5</t>
-  </si>
-  <si>
     <t xml:space="preserve">Колонка «Статус»: усі 19 рядків - «чернетка»</t>
   </si>
   <si>
@@ -1099,19 +1072,7 @@
     <t xml:space="preserve">Скрам-майстер / Аудитор-опонент</t>
   </si>
   <si>
-    <t xml:space="preserve">В6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Перший внесок і рахунок зарахування відсутні у калькуляторі (О-1), але обов'язкові для заявки (процес 3, крок 1) - заявка з калькулятора (О-4) виходить неповною</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Уточнити в замовника: перший внесок стає входом калькулятора (змінює P у US-01) чи додається на кроці подання (US-19). До відповіді US-19 лишається чернеткою</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КТ → замовник; питання - у docs/sprint1/audit.md (АО)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Зведення за статусами (формули рахують колонку G таблиці 1)</t>
+    <t xml:space="preserve">Зведення за статусами</t>
   </si>
   <si>
     <t xml:space="preserve">Усього stories</t>
@@ -1244,44 +1205,48 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1294,6 +1259,23 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1357,6 +1339,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
@@ -1365,34 +1351,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1537,21 +1523,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="46"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1561,7 +1547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1590,573 +1576,565 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="7" t="s">
         <v>16</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="B5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>22</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>24</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="B6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>28</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="7" t="s">
         <v>29</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="B7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="7" t="s">
         <v>35</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="B8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="7" t="s">
         <v>40</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="B9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>45</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="7" t="s">
         <v>46</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="8" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="6" t="s">
+      <c r="B10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="7" t="s">
         <v>50</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="7" t="s">
         <v>51</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="8" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="6" t="s">
+      <c r="B11" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="7" t="s">
         <v>56</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="7" t="s">
         <v>57</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="6" t="s">
+      <c r="B12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="7" t="s">
         <v>61</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="7" t="s">
         <v>62</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I12" s="8" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="6" t="s">
+      <c r="B13" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="7" t="s">
         <v>67</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="7" t="s">
         <v>68</v>
       </c>
       <c r="G13" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="8" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="6" t="s">
+      <c r="B14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="7" t="s">
         <v>73</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="7" t="s">
         <v>74</v>
       </c>
       <c r="G14" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="6" t="s">
+      <c r="B15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="7" t="s">
         <v>78</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="7" t="s">
         <v>79</v>
       </c>
       <c r="G15" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="8" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="7" t="s">
         <v>85</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="7" t="s">
         <v>86</v>
       </c>
       <c r="G16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="8" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="7" t="s">
         <v>91</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="7" t="s">
         <v>92</v>
       </c>
       <c r="G17" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="7" t="s">
         <v>96</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="7" t="s">
         <v>97</v>
       </c>
       <c r="G18" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="8" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="7" t="s">
         <v>103</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="7" t="s">
         <v>104</v>
       </c>
       <c r="G19" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="H19" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I19" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="I19" s="7" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
+      <c r="B20" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C20" s="6" t="s">
+      <c r="D20" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="E20" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="F20" s="7" t="s">
         <v>110</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>111</v>
       </c>
       <c r="G20" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H20" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="I20" s="7" t="s">
+      <c r="H20" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="D21" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="E21" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>116</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>117</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="I21" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
+      <c r="B22" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="6" t="s">
+      <c r="D22" s="7" t="s">
         <v>120</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>122</v>
+      <c r="F22" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="G22" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H22" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="I22" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="30" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="31" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="32" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="33" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="34" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="35" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="36" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="41" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="42" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="43" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="44" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="45" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="46" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="47" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+      <c r="I22" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A3:I22"/>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G4:G22" type="list">
+      <formula1>"чернетка,затверджено,відхилено"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2164,6 +2142,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2172,8 +2151,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46"/>
@@ -2182,161 +2161,128 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="30"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="C4" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D4" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E4" s="8"/>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="B5" s="8" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>339</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
         <v>340</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>341</v>
       </c>
-      <c r="E4" s="7"/>
-    </row>
-    <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="C6" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>345</v>
       </c>
-      <c r="E5" s="7"/>
-    </row>
-    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="E7" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="B6" s="7" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="E6" s="7"/>
-    </row>
-    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="E7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="E8" s="7"/>
-    </row>
-    <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="E9" s="7"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="B12" s="9" t="n">
+      <c r="B10" s="10" t="n">
         <f aca="false">COUNTA('Спринт 1'!A4:A22)</f>
         <v>19</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="9" t="n">
+      <c r="B11" s="10" t="n">
         <f aca="false">COUNTIF('Спринт 1'!G4:G22,"чернетка")</f>
         <v>19</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="B14" s="9" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="B12" s="10" t="n">
         <f aca="false">COUNTIF('Спринт 1'!G4:G22,"затверджено")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="B15" s="9" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="B13" s="10" t="n">
         <f aca="false">COUNTIF('Спринт 1'!G4:G22,"відхилено")</f>
         <v>0</v>
       </c>
@@ -2358,7 +2304,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52"/>
@@ -2366,117 +2312,115 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="4" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="B4" s="8" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="D4" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="D5" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="7" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C7" s="7" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="D8" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="D9" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="247.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
         <v>147</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="247.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
-        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2496,7 +2440,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
@@ -2505,138 +2449,136 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="D3" s="4" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="C4" s="8" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D4" s="7" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="C5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="E6" s="8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="E7" s="8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="B8" s="7" t="s">
+      <c r="D8" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B9" s="7" t="s">
+      <c r="D9" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
         <v>168</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="281.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="8" t="s">
-        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -2656,96 +2598,94 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C3" s="4" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="C4" s="8" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="C4" s="7" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="C5" s="7" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B6" s="7" t="s">
+      <c r="D6" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="C6" s="7" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="124.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="8" t="s">
-        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -2764,8 +2704,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
@@ -2773,299 +2713,292 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="70"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="D3" s="4" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="D4" s="7" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="D5" s="7" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D6" s="7" t="s">
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="D7" s="7" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="D8" s="7" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="D9" s="7" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="7" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D20" s="7" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C22" s="7" t="s">
+      <c r="D22" s="8" t="s">
         <v>219</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="281.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
-        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -3084,8 +3017,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
@@ -3093,383 +3026,376 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="70"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="D4" s="7" t="s">
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D5" s="7" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D6" s="7" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="D7" s="7" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="D8" s="7" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="D9" s="7" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="7" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C24" s="7" t="s">
+      <c r="D25" s="8" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="D24" s="7" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="7" t="s">
+      <c r="C26" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="D25" s="7" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D26" s="7" t="s">
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>250</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="348" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="s">
-        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -3488,8 +3414,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
@@ -3497,355 +3423,348 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="70"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="D4" s="7" t="s">
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="D7" s="8" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D6" s="7" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="7" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="D7" s="7" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D8" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="D9" s="7" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="7" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="D10" s="7" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="D11" s="7" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="D12" s="7" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="D13" s="7" t="s">
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D14" s="7" t="s">
+      <c r="D16" s="8" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D15" s="7" t="s">
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C16" s="7" t="s">
+      <c r="D17" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="D16" s="7" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C17" s="7" t="s">
+      <c r="C18" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="D17" s="7" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="7" t="s">
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>273</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D18" s="7" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D19" s="7" t="s">
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D20" s="7" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D21" s="7" t="s">
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="D22" s="7" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="7" t="s">
+    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>279</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="359.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
-        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -3864,8 +3783,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
@@ -3873,327 +3792,320 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="70"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="D4" s="7" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D5" s="7" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D6" s="7" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="D7" s="7" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="D8" s="7" t="s">
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="D9" s="7" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="7" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D16" s="7" t="s">
+      <c r="D21" s="8" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D17" s="7" t="s">
+      <c r="C22" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D18" s="7" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D19" s="7" t="s">
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>301</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="n">
-        <v>18</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="n">
-        <v>21</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="258.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="s">
-        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -4213,116 +4125,114 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultColWidth="8.68359375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="90"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B6" s="8" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="8" t="s">
         <v>321</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B14" s="8" t="s">
         <v>326</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>332</v>
       </c>
     </row>
   </sheetData>
